--- a/tests/fixtures/csvExcel/inventory.xlsx
+++ b/tests/fixtures/csvExcel/inventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="재고" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Inventory" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -13,31 +13,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
-    <t>매장명</t>
-  </si>
-  <si>
-    <t>상품명</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>재고수량</t>
-  </si>
-  <si>
-    <t>판매수량</t>
-  </si>
-  <si>
-    <t>판매기간시작일</t>
-  </si>
-  <si>
-    <t>판매기간종료일</t>
-  </si>
-  <si>
-    <t>본점</t>
-  </si>
-  <si>
-    <t>코카콜라 500ml</t>
+    <t>store</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>stock_qty</t>
+  </si>
+  <si>
+    <t>sales_qty</t>
+  </si>
+  <si>
+    <t>period_start</t>
+  </si>
+  <si>
+    <t>period_end</t>
+  </si>
+  <si>
+    <t>Main Store</t>
+  </si>
+  <si>
+    <t>Cola ½L</t>
   </si>
   <si>
     <t>SKU-COLA</t>
@@ -49,7 +49,7 @@
     <t>SKU-CHIPS</t>
   </si>
   <si>
-    <t>마카티점</t>
+    <t>North Branch</t>
   </si>
 </sst>
 </file>
@@ -476,7 +476,7 @@
         <v>46263</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
